--- a/doc/project_backlog_effort.xlsx
+++ b/doc/project_backlog_effort.xlsx
@@ -12,12 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一人排期" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三人预算" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估算依据" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story工数'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'一人排期'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三人预算'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'对照'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'估算依据'!$A$1:$C$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,11 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +57,18 @@
       <name val="Calibri"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +80,13 @@
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,11 +108,25 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFCBD9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFCBD9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFCBD9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFCBD9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,8 +138,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,6 +643,18 @@
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>报价人日 = 人数 × 迭代数 × 10；管理只计负责人，不乘全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>见第 8 节和「估算依据」表。人日没有改。</t>
         </is>
       </c>
     </row>
@@ -609,13 +669,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -639,6 +700,11 @@
           <t>人日</t>
         </is>
       </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -659,6 +725,11 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>一页验收假设，没有产品代码。按一个理想日，含写成和自己读一遍。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -679,6 +750,11 @@
       <c r="D3" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>在已经存在的帧上补失败用例，C 与 Pascal 各一套。三日是列向量、看到失败、补断言。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -699,6 +775,11 @@
       <c r="D4" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>登记自托管运行器并看到固件作业变绿。makefile 使用绝对路径，这一已知失败点使它不是 1 日就能结束的注册。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -719,6 +800,11 @@
       <c r="D5" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>两个工程按外设搬家并保持行为，再编 Debug 与 Release。这是重构，不是新功能，按 5 个理想日。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -739,6 +825,11 @@
       <c r="D6" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>系统测试的环境 3.0 人日，加上 P1 实机 70 小时（8.75 人日），合计 11.75，取整为 12。P2、长稳和 3 人日回归余量不在这里。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -759,6 +850,11 @@
       <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>只改 RX 的四路比较寄存器并核对波形，RA 不动。含先写失败测试和实机测量。系统测试里仅 PWM 波形一项就是 8 小时量级。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -779,6 +875,11 @@
       <c r="D8" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>这一族命令的第一个。proto、C、Pascal 的黄金字节和两块板都要动。5 日用来建立以后三条命令会复用的模式。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -799,6 +900,11 @@
       <c r="D9" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>模式已由 E2-S1 建立。这里只加地址和 1 字节，并先有非法地址的失败用例。按第一项的八成，取 4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -819,6 +925,11 @@
       <c r="D10" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>同样是跟随项。演示循环已经会发 Break 和 0x55，改成上位机给出的字节。4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -839,6 +950,11 @@
       <c r="D11" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>三条命令合成一次界面修改和一套黄金向量，不把协议税再付三遍。3 日。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -859,6 +975,11 @@
       <c r="D12" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>发送路径已经有了。新增的是接收邮箱、CanLog，以及分析仪上的实机。新的硬件路径按 8 日，不和 RA 平分。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -879,6 +1000,11 @@
       <c r="D13" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>接收路径完成后才做过滤。工作是通过和拒绝两个向量，加上两侧实现。5 日，低于新开一条接收路径。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -899,6 +1025,11 @@
       <c r="D14" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>CAN FD 的邮箱和经典 CAN 不是同一套寄存器。RX 的 8 日不能挪过来用。RA 再计 8 日。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -919,6 +1050,11 @@
       <c r="D15" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>环形缓冲先在主机上用同一组向量测完，固件再调用。256 帧、覆盖最旧、掉电不保留。不做 Flash，所以不是存储驱动的工时。6 日。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -939,6 +1075,11 @@
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>收发路径已经有了，只把帧放进缓冲，并在未连接时不发送。集成按 3 日。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -959,6 +1100,11 @@
       <c r="D17" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>分页和清空是新的编码，黄金字节要先失败再通过。板侧入库另计在 E4-S3。这里 5 日。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -979,6 +1125,11 @@
       <c r="D18" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>现状只有 USB 时钟和 D+ 上拉。8 日只覆盖承载同一套 HL1 字节的设备侧管道，不含 USB 认证和高吞吐。解析器复用 E0-S2。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -999,6 +1150,11 @@
       <c r="D19" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>RA 的 USB 控制器和 RX 不同，再计 8 日。UART 仍是验收通路，所以这 8 日失败时不把整份计划停住。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1019,6 +1175,11 @@
       <c r="D20" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>帧格式不变，编码测试仍走原来的一套。只加 COM 与 CDC 的选择。4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1039,6 +1200,11 @@
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PHY 地址、地址族和端口还没有客户确认。先写一页被后续测试引用的接口说明。1 日，不是协议栈。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1059,6 +1225,11 @@
       <c r="D22" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAC 地址和收发使能已经写下。10 日只覆盖静态地址上的一个周期 UDP 状态包，没有 TCP、网页和 TLS。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1079,6 +1250,11 @@
       <c r="D23" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>字节布局复用 RX 的测试，所以不是从零再设计报文。RGMII 和 PHY 尚未证实，比 RX 多 2 日，共 12 日。PHY 未就绪时停在字节测试，发布不因此改期。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1099,6 +1275,11 @@
       <c r="D24" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>用录好的 UDP 包驱动界面，不取代 HL1 命令通道。与选择 CDC 同级，4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1119,6 +1300,11 @@
       <c r="D25" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>每个 story 已经含自己的实机验收。这里是发布前再跑一轮既有 P1，并抽查新命令，仍按 12 日。不把 18.5 人日的当前测试再加一次。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1138,6 +1324,11 @@
       </c>
       <c r="D26" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>中日文档的主体已经在仓库里。3 日是按行为变化收口、打标签、确认发布产物，不是从零写规格。</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2314,10 +2505,10 @@
           <t>日历结束</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="8" t="n">
         <v>46661</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="8" t="n">
         <v>46437</v>
       </c>
     </row>
@@ -2413,4 +2604,416 @@
   <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>数字</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>E0-S1 最可能 1</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>O 0.8，P 1.5，期望 1.0。一页验收假设，没有产品代码。按一个理想日，含写成和自己读一遍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>E0-S2 最可能 3</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。在已经存在的帧上补失败用例，C 与 Pascal 各一套。三日是列向量、看到失败、补断言。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>E0-S4 最可能 2</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>O 1.4，P 3.6，期望 2.2。登记自托管运行器并看到固件作业变绿。makefile 使用绝对路径，这一已知失败点使它不是 1 日就能结束的注册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>E0-S5 最可能 5</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>O 3.8，P 7.5，期望 5.2。两个工程按外设搬家并保持行为，再编 Debug 与 Release。这是重构，不是新功能，按 5 个理想日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>E0-S3 最可能 12</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>O 8.4，P 21.6，期望 13.0。系统测试的环境 3.0 人日，加上 P1 实机 70 小时（8.75 人日），合计 11.75，取整为 12。P2、长稳和 3 人日回归余量不在这里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>E1-S1 最可能 3</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>O 2.1，P 5.4，期望 3.2。只改 RX 的四路比较寄存器并核对波形，RA 不动。含先写失败测试和实机测量。系统测试里仅 PWM 波形一项就是 8 小时量级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>E2-S1 最可能 5</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。这一族命令的第一个。proto、C、Pascal 的黄金字节和两块板都要动。5 日用来建立以后三条命令会复用的模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>E2-S2 最可能 4</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。模式已由 E2-S1 建立。这里只加地址和 1 字节，并先有非法地址的失败用例。按第一项的八成，取 4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>E2-S3 最可能 4</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。同样是跟随项。演示循环已经会发 Break 和 0x55，改成上位机给出的字节。4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>E2-S4 最可能 3</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。三条命令合成一次界面修改和一套黄金向量，不把协议税再付三遍。3 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>E3-S1 最可能 8</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。发送路径已经有了。新增的是接收邮箱、CanLog，以及分析仪上的实机。新的硬件路径按 8 日，不和 RA 平分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>E3-S2 最可能 8</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。CAN FD 的邮箱和经典 CAN 不是同一套寄存器。RX 的 8 日不能挪过来用。RA 再计 8 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>E3-S3 最可能 5</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。接收路径完成后才做过滤。工作是通过和拒绝两个向量，加上两侧实现。5 日，低于新开一条接收路径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>E4-S1 最可能 6</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>O 4.2，P 10.8，期望 6.5。环形缓冲先在主机上用同一组向量测完，固件再调用。256 帧、覆盖最旧、掉电不保留。不做 Flash，所以不是存储驱动的工时。6 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>E4-S2 最可能 5</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。分页和清空是新的编码，黄金字节要先失败再通过。板侧入库另计在 E4-S3。这里 5 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>E4-S3 最可能 3</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。收发路径已经有了，只把帧放进缓冲，并在未连接时不发送。集成按 3 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>E5-S1 最可能 8</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。现状只有 USB 时钟和 D+ 上拉。8 日只覆盖承载同一套 HL1 字节的设备侧管道，不含 USB 认证和高吞吐。解析器复用 E0-S2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>E5-S2 最可能 8</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。RA 的 USB 控制器和 RX 不同，再计 8 日。UART 仍是验收通路，所以这 8 日失败时不把整份计划停住。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>E5-S3 最可能 4</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。帧格式不变，编码测试仍走原来的一套。只加 COM 与 CDC 的选择。4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>E6-S1 最可能 1</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>O 0.8，P 1.5，期望 1.0。PHY 地址、地址族和端口还没有客户确认。先写一页被后续测试引用的接口说明。1 日，不是协议栈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>E6-S2 最可能 10</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>O 6.0，P 22.0，期望 11.3。MAC 地址和收发使能已经写下。10 日只覆盖静态地址上的一个周期 UDP 状态包，没有 TCP、网页和 TLS。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>E6-S3 最可能 12</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>O 7.2，P 26.4，期望 13.6。字节布局复用 RX 的测试，所以不是从零再设计报文。RGMII 和 PHY 尚未证实，比 RX 多 2 日，共 12 日。PHY 未就绪时停在字节测试，发布不因此改期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>E6-S4 最可能 4</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。用录好的 UDP 包驱动界面，不取代 HL1 命令通道。与选择 CDC 同级，4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>E7-S1 最可能 12</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>O 8.4，P 21.6，期望 13.0。每个 story 已经含自己的实机验收。这里是发布前再跑一轮既有 P1，并抽查新命令，仍按 12 日。不把 18.5 人日的当前测试再加一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>E7-S2 最可能 3</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。中日文档的主体已经在仓库里。3 日是按行为变化收口、打标签、确认发布产物，不是从零写规格。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>